--- a/data/trans_dic/P71_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P71_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad (tasa de respuesta: 99,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,15; 14,9</t>
+          <t>7,4; 15,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,72; 45,3</t>
+          <t>33,94; 45,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,96; 42,55</t>
+          <t>31,48; 43,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 8,06</t>
+          <t>2,96; 8,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,38; 19,42</t>
+          <t>10,83; 20,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,54; 45,74</t>
+          <t>33,64; 46,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,24; 37,3</t>
+          <t>25,91; 37,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,15; 15,21</t>
+          <t>6,08; 14,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,84; 15,95</t>
+          <t>9,88; 15,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35,53; 43,87</t>
+          <t>35,55; 44,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30,46; 38,18</t>
+          <t>30,08; 38,09</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,26; 9,73</t>
+          <t>5,27; 9,84</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,94; 28,76</t>
+          <t>20,7; 28,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49,11; 58,5</t>
+          <t>48,93; 58,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,65; 44,91</t>
+          <t>36,23; 44,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,18; 17,02</t>
+          <t>9,28; 17,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,41; 39,32</t>
+          <t>31,18; 39,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,34; 60,29</t>
+          <t>51,2; 60,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,23; 46,28</t>
+          <t>37,32; 46,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,2; 16,61</t>
+          <t>11,24; 16,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27,17; 33,05</t>
+          <t>27,13; 33,01</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51,55; 57,89</t>
+          <t>51,58; 58,22</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38,11; 44,33</t>
+          <t>38,05; 44,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,16; 15,79</t>
+          <t>11,24; 15,76</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,41; 21,0</t>
+          <t>12,06; 20,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,2; 20,29</t>
+          <t>12,14; 20,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,88; 29,66</t>
+          <t>20,05; 29,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,13; 19,88</t>
+          <t>11,27; 20,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,54; 31,05</t>
+          <t>20,76; 30,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,73; 18,72</t>
+          <t>10,71; 18,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,32; 37,83</t>
+          <t>27,48; 37,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,03; 23,17</t>
+          <t>16,23; 23,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,04; 24,61</t>
+          <t>18,08; 24,35</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,32; 18,04</t>
+          <t>12,47; 17,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25,24; 32,07</t>
+          <t>25,05; 32,12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,05; 20,61</t>
+          <t>14,84; 20,17</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,11; 15,82</t>
+          <t>8,99; 15,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,68; 30,3</t>
+          <t>20,91; 30,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,51; 35,38</t>
+          <t>25,67; 35,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,38; 15,88</t>
+          <t>7,0; 15,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,7; 27,59</t>
+          <t>19,15; 27,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,53; 30,45</t>
+          <t>21,95; 31,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,74; 43,47</t>
+          <t>33,5; 44,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,86; 58,84</t>
+          <t>18,41; 60,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,9; 20,08</t>
+          <t>15,02; 20,45</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,44; 28,75</t>
+          <t>22,73; 29,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,89; 38,13</t>
+          <t>31,22; 38,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,89; 47,06</t>
+          <t>14,76; 46,23</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,4; 20,54</t>
+          <t>10,5; 20,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27,43; 40,9</t>
+          <t>27,21; 40,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54,31; 67,96</t>
+          <t>54,41; 67,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,84; 8,68</t>
+          <t>3,0; 9,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,92; 28,28</t>
+          <t>15,95; 27,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,65; 42,74</t>
+          <t>29,72; 43,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,85; 72,28</t>
+          <t>59,62; 72,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 7,78</t>
+          <t>2,46; 8,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,37; 22,06</t>
+          <t>14,62; 22,52</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,37; 39,34</t>
+          <t>30,59; 39,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59,28; 68,23</t>
+          <t>58,71; 67,95</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,26; 7,14</t>
+          <t>3,23; 7,13</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,83; 25,44</t>
+          <t>15,37; 25,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,44; 21,66</t>
+          <t>12,36; 21,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,24; 24,03</t>
+          <t>13,79; 23,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,46; 16,08</t>
+          <t>8,62; 16,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,88; 37,83</t>
+          <t>26,85; 38,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,01; 19,85</t>
+          <t>11,52; 20,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,98; 23,63</t>
+          <t>14,03; 23,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,87; 18,79</t>
+          <t>11,74; 18,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,61; 30,16</t>
+          <t>22,59; 30,17</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,72; 19,15</t>
+          <t>12,65; 18,8</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15,24; 21,89</t>
+          <t>15,09; 21,76</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,17; 16,34</t>
+          <t>11,19; 16,03</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,06; 23,72</t>
+          <t>17,25; 23,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,29; 24,65</t>
+          <t>18,29; 24,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26,81; 34,58</t>
+          <t>26,83; 34,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,45; 16,02</t>
+          <t>9,67; 16,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>30,47; 38,52</t>
+          <t>30,58; 38,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,46; 27,11</t>
+          <t>20,42; 27,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,6; 36,94</t>
+          <t>29,56; 36,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,69; 15,04</t>
+          <t>4,91; 14,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,25; 30,6</t>
+          <t>24,97; 30,08</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20,11; 24,91</t>
+          <t>20,5; 25,17</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29,29; 34,6</t>
+          <t>29,43; 34,64</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,03; 13,91</t>
+          <t>7,47; 13,99</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,98; 21,6</t>
+          <t>15,9; 21,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>29,74; 36,5</t>
+          <t>29,59; 36,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29,8; 36,63</t>
+          <t>29,63; 36,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,79; 20,95</t>
+          <t>7,23; 21,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,34; 28,89</t>
+          <t>22,4; 28,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,16; 37,92</t>
+          <t>30,57; 37,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,3; 36,1</t>
+          <t>29,56; 36,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>19,7; 25,59</t>
+          <t>19,67; 25,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,75; 24,22</t>
+          <t>19,92; 24,18</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31,16; 35,9</t>
+          <t>30,99; 36,23</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30,25; 35,36</t>
+          <t>30,69; 35,26</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,33; 22,0</t>
+          <t>10,69; 21,93</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,6; 19,4</t>
+          <t>16,8; 19,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29,1; 32,22</t>
+          <t>28,99; 32,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31,94; 35,14</t>
+          <t>31,77; 35,16</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,65; 13,64</t>
+          <t>9,29; 13,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>26,34; 29,49</t>
+          <t>26,36; 29,5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,96; 33,27</t>
+          <t>29,9; 33,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,14; 37,32</t>
+          <t>33,97; 37,31</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,22; 22,23</t>
+          <t>13,86; 21,64</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>21,85; 23,98</t>
+          <t>22,05; 24,1</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29,95; 32,27</t>
+          <t>30,02; 32,22</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33,49; 35,86</t>
+          <t>33,58; 35,83</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12,82; 17,44</t>
+          <t>12,67; 17,28</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad (tasa de respuesta: 99,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19327; 40256</t>
+          <t>19979; 42178</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>99400; 133507</t>
+          <t>100031; 134731</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>90701; 124652</t>
+          <t>92234; 127251</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9678; 24990</t>
+          <t>9171; 25550</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26766; 50057</t>
+          <t>27923; 52187</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95635; 130422</t>
+          <t>95930; 132862</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75225; 106934</t>
+          <t>74289; 106659</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17804; 44040</t>
+          <t>17620; 42165</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>51928; 84194</t>
+          <t>52138; 84168</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>206008; 254422</t>
+          <t>206149; 256520</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>176592; 221346</t>
+          <t>174338; 220812</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31556; 58347</t>
+          <t>31590; 59035</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>101527; 139406</t>
+          <t>100358; 137964</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>246292; 293409</t>
+          <t>245381; 292914</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>177531; 223644</t>
+          <t>180416; 223334</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46876; 86922</t>
+          <t>47411; 90867</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>149090; 192731</t>
+          <t>152857; 193567</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>268315; 315116</t>
+          <t>267625; 315668</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>194020; 241221</t>
+          <t>194524; 241230</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>57489; 85259</t>
+          <t>57705; 84990</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>264910; 322232</t>
+          <t>264482; 321863</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>527991; 592843</t>
+          <t>528272; 596251</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>388422; 451815</t>
+          <t>387837; 453557</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>114271; 161711</t>
+          <t>115124; 161336</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>38887; 65769</t>
+          <t>37773; 65435</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39419; 65540</t>
+          <t>39210; 65388</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62182; 92769</t>
+          <t>62712; 90871</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34959; 62434</t>
+          <t>35390; 63304</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>70836; 102111</t>
+          <t>68267; 100361</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36474; 63638</t>
+          <t>36418; 61807</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91212; 126298</t>
+          <t>91750; 125502</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>55110; 79681</t>
+          <t>55819; 80938</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>115813; 158038</t>
+          <t>116082; 156334</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>81663; 119593</t>
+          <t>82687; 119277</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>163224; 207412</t>
+          <t>161981; 207674</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>98993; 135613</t>
+          <t>97642; 132681</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32515; 56426</t>
+          <t>32085; 56829</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>76904; 112688</t>
+          <t>77770; 113423</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94122; 130518</t>
+          <t>94714; 130615</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21694; 46684</t>
+          <t>20583; 45351</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>69168; 102075</t>
+          <t>70849; 101680</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>82722; 116999</t>
+          <t>84326; 120671</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>130355; 167948</t>
+          <t>129441; 170726</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>81299; 253604</t>
+          <t>79354; 259521</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>108277; 145894</t>
+          <t>109126; 148623</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>169628; 217348</t>
+          <t>171862; 221309</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>233324; 288019</t>
+          <t>235771; 288458</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>107956; 341211</t>
+          <t>106998; 335175</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>20772; 41029</t>
+          <t>20987; 40203</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>57784; 86161</t>
+          <t>57319; 86150</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>113652; 142212</t>
+          <t>113865; 141262</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5062; 15475</t>
+          <t>5351; 17015</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32030; 56896</t>
+          <t>32085; 55279</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>65109; 93855</t>
+          <t>65252; 94626</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>130149; 157170</t>
+          <t>129655; 156757</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6909; 19952</t>
+          <t>6303; 20870</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>57607; 88460</t>
+          <t>58609; 90322</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>130673; 169252</t>
+          <t>131617; 171372</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>252965; 291136</t>
+          <t>250540; 289931</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14147; 31025</t>
+          <t>14033; 30990</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>42545; 68386</t>
+          <t>41306; 68473</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>33971; 59141</t>
+          <t>33751; 58049</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37055; 62503</t>
+          <t>35873; 62231</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22813; 43355</t>
+          <t>23238; 44618</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>73630; 103611</t>
+          <t>73533; 104936</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30728; 55379</t>
+          <t>32149; 55852</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38181; 64548</t>
+          <t>38316; 65505</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>30470; 48202</t>
+          <t>30117; 48586</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>122726; 163691</t>
+          <t>122616; 163731</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>70236; 105700</t>
+          <t>69807; 103755</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>81263; 116732</t>
+          <t>80475; 116059</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>58765; 85991</t>
+          <t>58880; 84354</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>103114; 143373</t>
+          <t>104284; 144888</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>120971; 163022</t>
+          <t>120977; 162639</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>175716; 226689</t>
+          <t>175849; 224848</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>57969; 98261</t>
+          <t>59321; 99811</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>191167; 241645</t>
+          <t>191841; 241987</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>141943; 188088</t>
+          <t>141662; 189482</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>204351; 254996</t>
+          <t>204066; 252332</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>47795; 126331</t>
+          <t>41276; 123600</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>311090; 376950</t>
+          <t>307583; 370522</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>272512; 337591</t>
+          <t>277856; 341096</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>394216; 465660</t>
+          <t>396011; 466243</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>102106; 202122</t>
+          <t>108519; 203279</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>117064; 158282</t>
+          <t>116463; 157906</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>229855; 282123</t>
+          <t>228720; 282502</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>229365; 281964</t>
+          <t>228040; 279828</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>62833; 194011</t>
+          <t>66901; 196164</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>171035; 221208</t>
+          <t>171523; 219214</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>254949; 310326</t>
+          <t>250142; 308052</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>239585; 295174</t>
+          <t>241758; 294790</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>140436; 182445</t>
+          <t>140258; 181461</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>296011; 362881</t>
+          <t>298475; 362273</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>495733; 571273</t>
+          <t>493159; 576500</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>480242; 561300</t>
+          <t>487138; 559754</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>185621; 360613</t>
+          <t>175220; 359496</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>536405; 626782</t>
+          <t>542936; 627470</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>992066; 1098336</t>
+          <t>988394; 1099963</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1075363; 1183427</t>
+          <t>1069847; 1184093</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>329674; 465813</t>
+          <t>317457; 466090</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>873035; 977713</t>
+          <t>873730; 977973</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1061306; 1178750</t>
+          <t>1059267; 1179250</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1203999; 1316227</t>
+          <t>1198004; 1315886</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>518264; 809900</t>
+          <t>504971; 788405</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1429935; 1569869</t>
+          <t>1443179; 1577379</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2081858; 2243353</t>
+          <t>2087027; 2239782</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2308918; 2472259</t>
+          <t>2314822; 2470344</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>904865; 1231268</t>
+          <t>894116; 1219741</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P71_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P71_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,4; 15,61</t>
+          <t>7,42; 15,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,94; 45,71</t>
+          <t>33,9; 45,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,48; 43,44</t>
+          <t>31,13; 43,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 8,24</t>
+          <t>4,85; 10,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,83; 20,24</t>
+          <t>10,67; 19,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,64; 46,59</t>
+          <t>33,58; 45,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,91; 37,2</t>
+          <t>26,31; 37,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,08; 14,56</t>
+          <t>7,11; 13,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,88; 15,94</t>
+          <t>10,15; 16,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35,55; 44,24</t>
+          <t>35,6; 43,96</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30,08; 38,09</t>
+          <t>30,12; 38,57</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,27; 9,84</t>
+          <t>6,77; 11,21</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,7; 28,46</t>
+          <t>21,04; 28,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,93; 58,41</t>
+          <t>48,99; 58,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,23; 44,85</t>
+          <t>36,1; 45,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,28; 17,79</t>
+          <t>9,57; 16,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,18; 39,49</t>
+          <t>31,23; 39,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,2; 60,4</t>
+          <t>51,34; 60,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,32; 46,28</t>
+          <t>37,6; 46,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,24; 16,56</t>
+          <t>11,38; 16,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27,13; 33,01</t>
+          <t>26,91; 32,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51,58; 58,22</t>
+          <t>51,37; 58,09</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38,05; 44,5</t>
+          <t>37,71; 44,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,24; 15,76</t>
+          <t>11,41; 15,65</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,06; 20,89</t>
+          <t>12,3; 20,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,14; 20,24</t>
+          <t>12,15; 20,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,05; 29,05</t>
+          <t>20,01; 29,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,27; 20,16</t>
+          <t>12,53; 20,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,76; 30,52</t>
+          <t>20,89; 29,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,71; 18,18</t>
+          <t>10,68; 18,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,48; 37,59</t>
+          <t>27,72; 38,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,23; 23,54</t>
+          <t>16,74; 24,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,08; 24,35</t>
+          <t>18,11; 24,32</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,47; 17,99</t>
+          <t>12,6; 18,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25,05; 32,12</t>
+          <t>25,29; 32,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,84; 20,17</t>
+          <t>15,92; 21,34</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,99; 15,93</t>
+          <t>8,63; 15,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,91; 30,5</t>
+          <t>21,13; 30,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,67; 35,4</t>
+          <t>25,6; 35,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,0; 15,42</t>
+          <t>9,38; 19,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,15; 27,49</t>
+          <t>18,85; 27,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,95; 31,41</t>
+          <t>21,52; 30,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,5; 44,19</t>
+          <t>33,0; 43,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,41; 60,21</t>
+          <t>16,61; 24,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,02; 20,45</t>
+          <t>14,9; 20,55</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,73; 29,27</t>
+          <t>22,66; 29,3</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31,22; 38,19</t>
+          <t>30,91; 38,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,76; 46,23</t>
+          <t>14,43; 20,65</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,5; 20,12</t>
+          <t>10,54; 20,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27,21; 40,9</t>
+          <t>27,46; 41,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54,41; 67,51</t>
+          <t>54,39; 68,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,0; 9,55</t>
+          <t>4,32; 11,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,95; 27,47</t>
+          <t>15,96; 27,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,72; 43,09</t>
+          <t>29,69; 42,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,62; 72,09</t>
+          <t>60,18; 72,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 8,14</t>
+          <t>4,76; 10,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,62; 22,52</t>
+          <t>14,41; 22,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,59; 39,83</t>
+          <t>30,38; 39,85</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58,71; 67,95</t>
+          <t>59,48; 68,66</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 7,13</t>
+          <t>5,47; 9,82</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,37; 25,47</t>
+          <t>16,0; 26,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,36; 21,26</t>
+          <t>12,29; 21,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,79; 23,92</t>
+          <t>13,49; 23,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,62; 16,55</t>
+          <t>10,15; 17,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,85; 38,31</t>
+          <t>26,65; 37,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,52; 20,02</t>
+          <t>11,17; 20,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,03; 23,98</t>
+          <t>14,15; 23,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,74; 18,94</t>
+          <t>12,82; 20,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,59; 30,17</t>
+          <t>22,68; 30,14</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,65; 18,8</t>
+          <t>13,05; 19,44</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15,09; 21,76</t>
+          <t>15,17; 22,14</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,19; 16,03</t>
+          <t>12,46; 17,4</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,25; 23,97</t>
+          <t>17,03; 23,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,29; 24,59</t>
+          <t>18,03; 24,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26,83; 34,3</t>
+          <t>26,92; 34,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,67; 16,27</t>
+          <t>9,55; 15,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>30,58; 38,57</t>
+          <t>31,05; 38,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,42; 27,31</t>
+          <t>20,67; 27,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,56; 36,55</t>
+          <t>29,96; 37,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,91; 14,71</t>
+          <t>12,36; 17,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>24,97; 30,08</t>
+          <t>25,09; 30,32</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20,5; 25,17</t>
+          <t>20,2; 25,01</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29,43; 34,64</t>
+          <t>29,34; 34,58</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,47; 13,99</t>
+          <t>11,74; 15,4</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,9; 21,55</t>
+          <t>15,5; 21,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>29,59; 36,55</t>
+          <t>29,47; 36,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29,63; 36,35</t>
+          <t>29,6; 36,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,23; 21,19</t>
+          <t>18,66; 24,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,4; 28,63</t>
+          <t>22,58; 29,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,57; 37,65</t>
+          <t>30,89; 37,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,56; 36,05</t>
+          <t>29,48; 36,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>19,67; 25,45</t>
+          <t>20,65; 25,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,92; 24,18</t>
+          <t>19,96; 24,33</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30,99; 36,23</t>
+          <t>31,07; 35,92</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30,69; 35,26</t>
+          <t>30,63; 35,52</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,69; 21,93</t>
+          <t>20,3; 24,55</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,8; 19,42</t>
+          <t>16,71; 19,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>28,99; 32,27</t>
+          <t>29,01; 32,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31,77; 35,16</t>
+          <t>31,84; 35,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,29; 13,64</t>
+          <t>13,0; 15,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>26,36; 29,5</t>
+          <t>26,32; 29,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,9; 33,29</t>
+          <t>29,96; 33,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33,97; 37,31</t>
+          <t>34,08; 37,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,86; 21,64</t>
+          <t>15,73; 18,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>22,05; 24,1</t>
+          <t>22,0; 24,11</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30,02; 32,22</t>
+          <t>29,98; 32,31</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33,58; 35,83</t>
+          <t>33,44; 35,81</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12,67; 17,28</t>
+          <t>14,73; 16,53</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15652</t>
+          <t>23766</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26835</t>
+          <t>30255</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42487</t>
+          <t>54021</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19979; 42178</t>
+          <t>20034; 40993</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>100031; 134731</t>
+          <t>99927; 134299</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92234; 127251</t>
+          <t>91205; 126308</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9171; 25550</t>
+          <t>15405; 33200</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27923; 52187</t>
+          <t>27517; 51453</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95930; 132862</t>
+          <t>95762; 131103</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>74289; 106659</t>
+          <t>75430; 107147</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17620; 42165</t>
+          <t>22480; 42918</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>52138; 84168</t>
+          <t>53614; 85921</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>206149; 256520</t>
+          <t>206465; 254915</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>174338; 220812</t>
+          <t>174568; 223564</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31590; 59035</t>
+          <t>42912; 71013</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65908</t>
+          <t>67250</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>70402</t>
+          <t>76139</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>136310</t>
+          <t>143389</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>100358; 137964</t>
+          <t>101983; 139893</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>245381; 292914</t>
+          <t>245691; 291388</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>180416; 223334</t>
+          <t>179803; 224833</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47411; 90867</t>
+          <t>50102; 87631</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>152857; 193567</t>
+          <t>153076; 194223</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>267625; 315668</t>
+          <t>268346; 316164</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>194524; 241230</t>
+          <t>195993; 241314</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>57705; 84990</t>
+          <t>61955; 92337</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>264482; 321863</t>
+          <t>262401; 320207</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>528272; 596251</t>
+          <t>526066; 594905</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>387837; 453557</t>
+          <t>384394; 451880</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>115124; 161336</t>
+          <t>121864; 167117</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47266</t>
+          <t>50937</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>67289</t>
+          <t>71784</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>114555</t>
+          <t>122721</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>37773; 65435</t>
+          <t>38522; 65159</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39210; 65388</t>
+          <t>39242; 67075</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62712; 90871</t>
+          <t>62584; 91331</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35390; 63304</t>
+          <t>39164; 64508</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>68267; 100361</t>
+          <t>68698; 98589</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36418; 61807</t>
+          <t>36325; 62983</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91750; 125502</t>
+          <t>92554; 127178</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>55819; 80938</t>
+          <t>58787; 85061</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>116082; 156334</t>
+          <t>116309; 156183</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>82687; 119277</t>
+          <t>83546; 119997</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>161981; 207674</t>
+          <t>163511; 208098</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>97642; 132681</t>
+          <t>105702; 141629</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31363</t>
+          <t>48324</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>141495</t>
+          <t>83553</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>172859</t>
+          <t>131877</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32085; 56829</t>
+          <t>30805; 55988</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>77770; 113423</t>
+          <t>78564; 113806</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94714; 130615</t>
+          <t>94441; 130966</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20583; 45351</t>
+          <t>33037; 68767</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>70849; 101680</t>
+          <t>69734; 101323</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>84326; 120671</t>
+          <t>82676; 116593</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>129441; 170726</t>
+          <t>127518; 168600</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>79354; 259521</t>
+          <t>67833; 100128</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>109126; 148623</t>
+          <t>108277; 149367</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>171862; 221309</t>
+          <t>171351; 221507</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>235771; 288458</t>
+          <t>233482; 287884</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>106998; 335175</t>
+          <t>109732; 156999</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9061</t>
+          <t>15238</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>16325</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>22002</t>
+          <t>31563</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>20987; 40203</t>
+          <t>21064; 40276</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>57319; 86150</t>
+          <t>57853; 87002</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>113865; 141262</t>
+          <t>113806; 142890</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5351; 17015</t>
+          <t>8860; 23581</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32085; 55279</t>
+          <t>32108; 55968</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>65252; 94626</t>
+          <t>65203; 94338</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>129655; 156757</t>
+          <t>130856; 158122</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6303; 20870</t>
+          <t>10777; 24118</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>58609; 90322</t>
+          <t>57767; 88227</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>131617; 171372</t>
+          <t>130723; 171474</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>250540; 289931</t>
+          <t>253826; 292959</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14033; 30990</t>
+          <t>23579; 42371</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32092</t>
+          <t>36688</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>39041</t>
+          <t>42258</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>71133</t>
+          <t>78946</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>41306; 68473</t>
+          <t>43010; 70624</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>33751; 58049</t>
+          <t>33548; 58208</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35873; 62231</t>
+          <t>35080; 61939</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23238; 44618</t>
+          <t>27490; 48397</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>73533; 104936</t>
+          <t>72980; 103353</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32149; 55852</t>
+          <t>31158; 57406</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38316; 65505</t>
+          <t>38647; 64128</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>30117; 48586</t>
+          <t>33744; 52723</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>122616; 163731</t>
+          <t>123065; 163559</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69807; 103755</t>
+          <t>72037; 107298</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>80475; 116059</t>
+          <t>80907; 118071</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>58880; 84354</t>
+          <t>66517; 92896</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>75852</t>
+          <t>85240</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>89830</t>
+          <t>111544</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>165682</t>
+          <t>196784</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>104284; 144888</t>
+          <t>102939; 142750</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>120977; 162639</t>
+          <t>119284; 164635</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>175849; 224848</t>
+          <t>176422; 225503</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>59321; 99811</t>
+          <t>67267; 106394</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>191841; 241987</t>
+          <t>194792; 242079</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>141662; 189482</t>
+          <t>143413; 189208</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>204066; 252332</t>
+          <t>206840; 257454</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>41276; 123600</t>
+          <t>93980; 129710</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>307583; 370522</t>
+          <t>309063; 373532</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>277856; 341096</t>
+          <t>273788; 339002</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>396011; 466243</t>
+          <t>394838; 465411</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>108519; 203279</t>
+          <t>171973; 225641</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>137204</t>
+          <t>171296</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>159735</t>
+          <t>191722</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>296939</t>
+          <t>363018</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>116463; 157906</t>
+          <t>113547; 156576</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>228720; 282502</t>
+          <t>227754; 282617</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>228040; 279828</t>
+          <t>227837; 281709</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>66901; 196164</t>
+          <t>148337; 198036</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>171523; 219214</t>
+          <t>172900; 222497</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>250142; 308052</t>
+          <t>252774; 307811</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>241758; 294790</t>
+          <t>241117; 294897</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>140258; 181461</t>
+          <t>170788; 213852</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>298475; 362273</t>
+          <t>299046; 364524</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>493159; 576500</t>
+          <t>494435; 571601</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>487138; 559754</t>
+          <t>486172; 563911</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>175220; 359496</t>
+          <t>329243; 398323</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>414398</t>
+          <t>498739</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>607568</t>
+          <t>623580</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1021966</t>
+          <t>1122320</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>542936; 627470</t>
+          <t>539752; 628141</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>988394; 1099963</t>
+          <t>989070; 1096750</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1069847; 1184093</t>
+          <t>1072306; 1181665</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>317457; 466090</t>
+          <t>452722; 545741</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>873730; 977973</t>
+          <t>872523; 974556</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1059267; 1179250</t>
+          <t>1061488; 1178397</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1198004; 1315886</t>
+          <t>1201964; 1319856</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>504971; 788405</t>
+          <t>581647; 665420</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1443179; 1577379</t>
+          <t>1440326; 1578494</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2087027; 2239782</t>
+          <t>2084308; 2246181</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2314822; 2470344</t>
+          <t>2305668; 2468465</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>894116; 1219741</t>
+          <t>1057634; 1186356</t>
         </is>
       </c>
     </row>
